--- a/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/ru-ru.xlsx
+++ b/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/ru-ru.xlsx
@@ -5,10 +5,10 @@
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Documents\_Learn\Packaging.tutorial\OS.11\24H2\Expand\Install\Report\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5924f5d6bcb7c7fc/Documents/_Learn/Packaging.tutorial/OS.11/24H2/Expand/Install/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130DBBC2-1D15-4665-B708-1F2260508552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{130DBBC2-1D15-4665-B708-1F2260508552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9137DAB-B9E3-4856-8D1D-10107AAF87DE}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4894,11 +4894,12 @@
       <c r="C8" s="14"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="15"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" spans="1:12" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B9" s="17"/>
@@ -4908,6 +4909,7 @@
       <c r="D9" s="19" t="s">
         <v>4</v>
       </c>
+      <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:12" ht="42" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="20"/>
@@ -5190,7 +5192,7 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <dataConsolidate/>
-  <conditionalFormatting sqref="F8:I1048576 F1:I1 H2:J5">
+  <conditionalFormatting sqref="F12:I1048576 F1:I1 H2:J5">
     <cfRule type="iconSet" priority="282">
       <iconSet iconSet="3Symbols2" showValue="0">
         <cfvo type="percent" val="0"/>
@@ -5209,7 +5211,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8:I8 H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:J7" xr:uid="{23AE6323-BC7F-40E9-A5AD-9DE77137CC3B}">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
